--- a/Proyecto Interno/review-food-security-paper/02_models/coca/coca_results.xlsx
+++ b/Proyecto Interno/review-food-security-paper/02_models/coca/coca_results.xlsx
@@ -420,7 +420,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>610.482997719795</v>
+        <v>610.4829977197951</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -431,10 +431,10 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1566.339179084892</v>
+        <v>1566.339179084891</v>
       </c>
       <c r="F2">
-        <v>712.7048878307556</v>
+        <v>712.7048878307555</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>589.8355717768138</v>
+        <v>589.8355717768139</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>794.7190047265083</v>
+        <v>794.7190047265084</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>610.482997719795</v>
+        <v>610.4829977197951</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -548,7 +548,7 @@
         <v>1552.721560558909</v>
       </c>
       <c r="F5">
-        <v>706.5086926428444</v>
+        <v>706.5086926428445</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -621,10 +621,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2021.313186171892</v>
+        <v>2021.313186171893</v>
       </c>
       <c r="F7">
-        <v>706.5086926428444</v>
+        <v>706.5086926428445</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>610.4829977197951</v>
+        <v>610.482997719795</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>1552.095463155703</v>
       </c>
       <c r="F8">
-        <v>706.2238101056001</v>
+        <v>706.2238101056</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>589.8355717768139</v>
+        <v>589.8355717768138</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>1499.601329409732</v>
       </c>
       <c r="F9">
-        <v>706.2238101056001</v>
+        <v>706.2238101056</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>589.8355717768139</v>
+        <v>589.8355717768138</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>1515.782989579547</v>
       </c>
       <c r="F12">
-        <v>713.8444179797334</v>
+        <v>713.8444179797333</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>794.7190047265084</v>
+        <v>794.7190047265082</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>2042.300611391138</v>
       </c>
       <c r="F13">
-        <v>713.8444179797333</v>
+        <v>713.8444179797332</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>589.8355717768138</v>
+        <v>589.8355717768139</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>2043.523179850038</v>
       </c>
       <c r="F16">
-        <v>714.2717417856001</v>
+        <v>714.2717417856002</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>610.482997719795</v>
+        <v>610.4829977197951</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>1577.76545669809</v>
+        <v>1577.765456698091</v>
       </c>
       <c r="F17">
-        <v>717.9039941375997</v>
+        <v>717.9039941376002</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>1524.403126306835</v>
       </c>
       <c r="F18">
-        <v>717.9039941375997</v>
+        <v>717.9039941376001</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>794.7190047265082</v>
+        <v>794.7190047265084</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>2053.915011756786</v>
+        <v>2053.915011756787</v>
       </c>
       <c r="F19">
-        <v>717.9039941375995</v>
+        <v>717.9039941376002</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>589.8355717768139</v>
+        <v>589.835571776814</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>1532.115880218182</v>
       </c>
       <c r="F24">
-        <v>721.5362464881778</v>
+        <v>721.5362464881779</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>610.4829977197951</v>
+        <v>610.482997719795</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>1583.869906380912</v>
       </c>
       <c r="F29">
-        <v>720.6815988764445</v>
+        <v>720.6815988764444</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>2061.861706741668</v>
       </c>
       <c r="F31">
-        <v>720.6815988764445</v>
+        <v>720.6815988764444</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>1597.957097959299</v>
       </c>
       <c r="F32">
-        <v>727.0914559672889</v>
+        <v>727.091455967289</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>589.8355717768139</v>
+        <v>589.8355717768138</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>1543.911856792207</v>
       </c>
       <c r="F33">
-        <v>727.0914559672889</v>
+        <v>727.091455967289</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>794.7190047265084</v>
+        <v>794.7190047265083</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>2080.200233633298</v>
       </c>
       <c r="F34">
-        <v>727.0914559672889</v>
+        <v>727.091455967289</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
         <v>1</v>
       </c>
       <c r="E35">
-        <v>1597.800573606935</v>
+        <v>1597.800573606934</v>
       </c>
       <c r="F35">
-        <v>727.0202353322667</v>
+        <v>727.0202353322666</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="B36">
-        <v>589.8355717768139</v>
+        <v>589.8355717768138</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>1543.760626321877</v>
       </c>
       <c r="F36">
-        <v>727.0202353322668</v>
+        <v>727.0202353322666</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>794.7190047265084</v>
+        <v>794.7190047265082</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>2079.996472221447</v>
+        <v>2079.996472221446</v>
       </c>
       <c r="F37">
-        <v>727.0202353322667</v>
+        <v>727.0202353322665</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>610.4829977197951</v>
+        <v>610.482997719795</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>1600.14843887052</v>
       </c>
       <c r="F38">
-        <v>728.0885448476445</v>
+        <v>728.0885448476444</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="B39">
-        <v>589.835571776814</v>
+        <v>589.8355717768139</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>1546.029083355692</v>
       </c>
       <c r="F39">
-        <v>728.0885448476446</v>
+        <v>728.0885448476445</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>2083.052893370731</v>
+        <v>2083.05289337073</v>
       </c>
       <c r="F40">
-        <v>728.0885448476445</v>
+        <v>728.0885448476444</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>1597.800573606935</v>
       </c>
       <c r="F41">
-        <v>727.0202353322669</v>
+        <v>727.0202353322667</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B42">
-        <v>589.8355717768138</v>
+        <v>589.8355717768139</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>2079.996472221448</v>
+        <v>2079.996472221447</v>
       </c>
       <c r="F43">
-        <v>727.0202353322669</v>
+        <v>727.0202353322667</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>1625.661908062106</v>
       </c>
       <c r="F44">
-        <v>739.6975082453336</v>
+        <v>739.6975082453333</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="B45">
-        <v>589.8355717768139</v>
+        <v>589.8355717768138</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
         <v>1</v>
       </c>
       <c r="E45">
-        <v>1570.679649783975</v>
+        <v>1570.679649783974</v>
       </c>
       <c r="F45">
-        <v>739.6975082453336</v>
+        <v>739.6975082453332</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2103,10 +2103,10 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>2116.266003185075</v>
+        <v>2116.266003185074</v>
       </c>
       <c r="F46">
-        <v>739.6975082453334</v>
+        <v>739.6975082453333</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>1635.522942164164</v>
       </c>
       <c r="F50">
-        <v>744.1844082076444</v>
+        <v>744.1844082076445</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="B51">
-        <v>589.8355717768139</v>
+        <v>589.8355717768138</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="B52">
-        <v>794.7190047265084</v>
+        <v>794.7190047265083</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="B54">
-        <v>589.8355717768138</v>
+        <v>589.8355717768139</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>1575.972716194196</v>
       </c>
       <c r="F54">
-        <v>742.1902304469334</v>
+        <v>742.1902304469335</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="B57">
-        <v>589.8355717768139</v>
+        <v>589.8355717768138</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>1562.966895869608</v>
       </c>
       <c r="F57">
-        <v>736.0652558933335</v>
+        <v>736.0652558933333</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="B58">
-        <v>794.7190047265084</v>
+        <v>794.7190047265082</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>2105.874171278325</v>
       </c>
       <c r="F58">
-        <v>736.0652558933334</v>
+        <v>736.0652558933333</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="B60">
-        <v>589.8355717768139</v>
+        <v>589.8355717768138</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>1562.664434931967</v>
       </c>
       <c r="F60">
-        <v>735.9228146247111</v>
+        <v>735.922814624711</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>2105.466648458692</v>
       </c>
       <c r="F61">
-        <v>735.9228146247112</v>
+        <v>735.9228146247111</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="B63">
-        <v>589.8355717768138</v>
+        <v>589.8355717768139</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>1549.053692732098</v>
       </c>
       <c r="F63">
-        <v>729.5129575338666</v>
+        <v>729.5129575338667</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="B64">
-        <v>794.7190047265083</v>
+        <v>794.7190047265084</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2787,10 +2787,10 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>2087.128121567061</v>
+        <v>2087.128121567062</v>
       </c>
       <c r="F64">
-        <v>729.5129575338666</v>
+        <v>729.5129575338667</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2825,10 +2825,10 @@
         <v>1</v>
       </c>
       <c r="E65">
-        <v>1590.913502168543</v>
+        <v>1590.913502168542</v>
       </c>
       <c r="F65">
-        <v>723.8865274211555</v>
+        <v>723.8865274211554</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2863,10 +2863,10 @@
         <v>1</v>
       </c>
       <c r="E66">
-        <v>1537.106485690763</v>
+        <v>1537.106485690762</v>
       </c>
       <c r="F66">
-        <v>723.8865274211556</v>
+        <v>723.8865274211555</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="B67">
-        <v>794.7190047265083</v>
+        <v>794.7190047265084</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>2071.030970185448</v>
       </c>
       <c r="F67">
-        <v>723.8865274211555</v>
+        <v>723.8865274211553</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="B69">
-        <v>589.8355717768138</v>
+        <v>589.8355717768139</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>1567.655040404548</v>
       </c>
       <c r="F69">
-        <v>738.273095557689</v>
+        <v>738.2730955576891</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="B70">
-        <v>794.7190047265083</v>
+        <v>794.7190047265084</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3167,10 +3167,10 @@
         <v>1</v>
       </c>
       <c r="E74">
-        <v>1597.331000556093</v>
+        <v>1597.331000556094</v>
       </c>
       <c r="F74">
-        <v>726.8065734300446</v>
+        <v>726.8065734300448</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>1543.306934916926</v>
       </c>
       <c r="F75">
-        <v>726.8065734300445</v>
+        <v>726.8065734300448</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3243,10 +3243,10 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>2079.385187994032</v>
+        <v>2079.385187994033</v>
       </c>
       <c r="F76">
-        <v>726.8065734300445</v>
+        <v>726.8065734300448</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="B77">
-        <v>610.482997719795</v>
+        <v>610.4829977197951</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>1577.921981047329</v>
       </c>
       <c r="F77">
-        <v>717.9752147711999</v>
+        <v>717.9752147712002</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="B78">
-        <v>589.8355717768138</v>
+        <v>589.8355717768139</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>1524.554356774146</v>
       </c>
       <c r="F78">
-        <v>717.9752147712001</v>
+        <v>717.9752147712002</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="B79">
-        <v>794.7190047265083</v>
+        <v>794.7190047265084</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>2054.118773164569</v>
       </c>
       <c r="F79">
-        <v>717.9752147711999</v>
+        <v>717.9752147712001</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>1572.287104415349</v>
       </c>
       <c r="F80">
-        <v>715.4112719345777</v>
+        <v>715.4112719345776</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>1</v>
       </c>
       <c r="E81">
-        <v>1519.110059893594</v>
+        <v>1519.110059893593</v>
       </c>
       <c r="F81">
         <v>715.4112719345776</v>
@@ -3471,10 +3471,10 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>2046.783362407103</v>
+        <v>2046.783362407102</v>
       </c>
       <c r="F82">
-        <v>715.4112719345777</v>
+        <v>715.4112719345776</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="B92">
-        <v>610.482997719795</v>
+        <v>610.4829977197951</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>1648.357938936139</v>
       </c>
       <c r="F92">
-        <v>750.0245002240002</v>
+        <v>750.0245002240001</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>1592.608067770472</v>
       </c>
       <c r="F93">
-        <v>750.0245002240002</v>
+        <v>750.0245002240001</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3927,10 +3927,10 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>2145.811407618652</v>
+        <v>2145.811407618651</v>
       </c>
       <c r="F94">
-        <v>750.0245002240002</v>
+        <v>750.0245002240001</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="B95">
-        <v>610.482997719795</v>
+        <v>610.4829977197951</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1707.524143560989</v>
       </c>
       <c r="F95">
-        <v>776.9459000035556</v>
+        <v>776.9459000035557</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="B96">
-        <v>589.8355717768138</v>
+        <v>589.8355717768139</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>1649.773185005695</v>
       </c>
       <c r="F96">
-        <v>776.9459000035556</v>
+        <v>776.9459000035557</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>1716.289507208999</v>
       </c>
       <c r="F98">
-        <v>780.9342555264001</v>
+        <v>780.9342555264002</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="B99">
-        <v>589.8355717768139</v>
+        <v>589.8355717768138</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="B100">
-        <v>794.7190047265084</v>
+        <v>794.7190047265083</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="B101">
-        <v>610.482997719795</v>
+        <v>610.4829977197951</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -4193,10 +4193,10 @@
         <v>1</v>
       </c>
       <c r="E101">
-        <v>1729.281028333338</v>
+        <v>1729.281028333339</v>
       </c>
       <c r="F101">
-        <v>786.8455681777777</v>
+        <v>786.8455681777779</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="B104">
-        <v>610.4829977197951</v>
+        <v>610.482997719795</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -4307,10 +4307,10 @@
         <v>1</v>
       </c>
       <c r="E104">
-        <v>1745.87260952455</v>
+        <v>1745.872609524549</v>
       </c>
       <c r="F104">
-        <v>794.3949554176</v>
+        <v>794.3949554175999</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="B105">
-        <v>589.8355717768139</v>
+        <v>589.8355717768138</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>1686.824649883284</v>
       </c>
       <c r="F105">
-        <v>794.3949554175999</v>
+        <v>794.3949554175998</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="B106">
-        <v>794.7190047265084</v>
+        <v>794.7190047265083</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -4383,10 +4383,10 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>2272.754765985243</v>
+        <v>2272.754765985242</v>
       </c>
       <c r="F106">
-        <v>794.3949554175999</v>
+        <v>794.3949554175998</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5105,10 +5105,10 @@
         <v>1</v>
       </c>
       <c r="E125">
-        <v>2007.424799815455</v>
+        <v>2007.424799815454</v>
       </c>
       <c r="F125">
-        <v>913.4046353976888</v>
+        <v>913.4046353976887</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="B126">
-        <v>589.8355717768138</v>
+        <v>589.8355717768139</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="B127">
-        <v>794.7190047265083</v>
+        <v>794.7190047265084</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -5181,10 +5181,10 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>2613.240081920989</v>
+        <v>2613.24008192099</v>
       </c>
       <c r="F127">
-        <v>913.4046353976887</v>
+        <v>913.4046353976888</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -5219,10 +5219,10 @@
         <v>1</v>
       </c>
       <c r="E128">
-        <v>2025.268575813078</v>
+        <v>2025.268575813079</v>
       </c>
       <c r="F128">
-        <v>921.5237877119998</v>
+        <v>921.5237877120002</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>1956.771036831754</v>
       </c>
       <c r="F129">
-        <v>921.5237877119998</v>
+        <v>921.5237877120002</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -5295,10 +5295,10 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <v>2636.468882648217</v>
+        <v>2636.468882648218</v>
       </c>
       <c r="F130">
-        <v>921.5237877119998</v>
+        <v>921.5237877120001</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="B131">
-        <v>610.4829977197949</v>
+        <v>610.482997719795</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -5447,10 +5447,10 @@
         <v>1</v>
       </c>
       <c r="E134">
-        <v>2306.229785612747</v>
+        <v>2306.229785612748</v>
       </c>
       <c r="F134">
-        <v>1049.364826350933</v>
+        <v>1049.364826350934</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="B136">
-        <v>794.7190047265084</v>
+        <v>794.7190047265083</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="B137">
-        <v>610.4829977197949</v>
+        <v>610.482997719795</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="B138">
-        <v>589.8355717768138</v>
+        <v>589.8355717768139</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="E138">
-        <v>2254.997521463214</v>
+        <v>2254.997521463215</v>
       </c>
       <c r="F138">
         <v>1061.970878628978</v>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="B139">
-        <v>794.7190047265082</v>
+        <v>794.7190047265083</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="E139">
-        <v>3038.286382965203</v>
+        <v>3038.286382965204</v>
       </c>
       <c r="F139">
         <v>1061.970878628978</v>
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="B140">
-        <v>610.482997719795</v>
+        <v>610.4829977197951</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="B141">
-        <v>589.8355717768139</v>
+        <v>589.835571776814</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="B146">
-        <v>610.4829977197951</v>
+        <v>610.482997719795</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="E148">
-        <v>3277.706039591239</v>
+        <v>3277.706039591238</v>
       </c>
       <c r="F148">
         <v>1145.655123976533</v>
@@ -6017,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="E149">
-        <v>2571.225511624411</v>
+        <v>2571.225511624412</v>
       </c>
       <c r="F149">
         <v>1169.941360287289</v>
@@ -6055,7 +6055,7 @@
         <v>1</v>
       </c>
       <c r="E150">
-        <v>2484.262912285427</v>
+        <v>2484.262912285428</v>
       </c>
       <c r="F150">
         <v>1169.941360287289</v>
@@ -6093,7 +6093,7 @@
         <v>0</v>
       </c>
       <c r="E151">
-        <v>3347.188680369209</v>
+        <v>3347.18868036921</v>
       </c>
       <c r="F151">
         <v>1169.941360287289</v>
@@ -6131,7 +6131,7 @@
         <v>1</v>
       </c>
       <c r="E152">
-        <v>2607.539161022865</v>
+        <v>2607.539161022864</v>
       </c>
       <c r="F152">
         <v>1186.464547453156</v>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="B153">
-        <v>589.835571776814</v>
+        <v>589.8355717768139</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>1</v>
       </c>
       <c r="E153">
-        <v>2519.348381063824</v>
+        <v>2519.348381063823</v>
       </c>
       <c r="F153">
         <v>1186.464547453156</v>
@@ -6207,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="E154">
-        <v>3394.461327462933</v>
+        <v>3394.461327462932</v>
       </c>
       <c r="F154">
         <v>1186.464547453156</v>
@@ -6272,7 +6272,7 @@
         </is>
       </c>
       <c r="B156">
-        <v>589.835571776814</v>
+        <v>589.8355717768139</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>1</v>
       </c>
       <c r="E156">
-        <v>2565.776135011293</v>
+        <v>2565.776135011292</v>
       </c>
       <c r="F156">
         <v>1208.329282195911</v>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="E157">
-        <v>3457.016080303071</v>
+        <v>3457.01608030307</v>
       </c>
       <c r="F157">
         <v>1208.329282195911</v>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="B158">
-        <v>578.3523136292796</v>
+        <v>578.3523136292795</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         </is>
       </c>
       <c r="B159">
-        <v>558.7915943148763</v>
+        <v>558.7915943148764</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>1</v>
       </c>
       <c r="E159">
-        <v>2575.711138890032</v>
+        <v>2575.711138890033</v>
       </c>
       <c r="F159">
         <v>1213.008083257937</v>
@@ -6587,7 +6587,7 @@
         <v>1</v>
       </c>
       <c r="E164">
-        <v>2546.380862224005</v>
+        <v>2546.380862224006</v>
       </c>
       <c r="F164">
         <v>1158.63671867419</v>
@@ -6614,7 +6614,7 @@
         </is>
       </c>
       <c r="B165">
-        <v>558.7915943148763</v>
+        <v>558.7915943148764</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>1</v>
       </c>
       <c r="E165">
-        <v>2460.258545186887</v>
+        <v>2460.258545186888</v>
       </c>
       <c r="F165">
         <v>1158.63671867419</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="B167">
-        <v>578.3523136292796</v>
+        <v>578.3523136292795</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>1</v>
       </c>
       <c r="E167">
-        <v>2483.617953648761</v>
+        <v>2483.61795364876</v>
       </c>
       <c r="F167">
         <v>1130.078771383242</v>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="B168">
-        <v>558.7915943148763</v>
+        <v>558.7915943148764</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>1</v>
       </c>
       <c r="E170">
-        <v>2312.935446430637</v>
+        <v>2312.935446430636</v>
       </c>
       <c r="F170">
         <v>1052.415990048337</v>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="B173">
-        <v>578.3523136292795</v>
+        <v>578.3523136292796</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>1</v>
       </c>
       <c r="E173">
-        <v>2293.536001962463</v>
+        <v>2293.536001962464</v>
       </c>
       <c r="F173">
         <v>1043.588988158653</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="B174">
-        <v>558.7915943148762</v>
+        <v>558.7915943148764</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -6967,10 +6967,10 @@
         <v>1</v>
       </c>
       <c r="E174">
-        <v>2215.965267109963</v>
+        <v>2215.965267109964</v>
       </c>
       <c r="F174">
-        <v>1043.588988158652</v>
+        <v>1043.588988158653</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         </is>
       </c>
       <c r="B175">
-        <v>752.891688688271</v>
+        <v>752.8916886882711</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="B176">
-        <v>578.3523136292795</v>
+        <v>578.3523136292796</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="B178">
-        <v>752.8916886882711</v>
+        <v>752.891688688271</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="E178">
-        <v>2948.557845241137</v>
+        <v>2948.557845241136</v>
       </c>
       <c r="F178">
         <v>1030.608103026526</v>
@@ -7160,7 +7160,7 @@
         <v>2258.649606027478</v>
       </c>
       <c r="F179">
-        <v>1027.715220054232</v>
+        <v>1027.715220054231</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -7195,10 +7195,10 @@
         <v>1</v>
       </c>
       <c r="E180">
-        <v>2182.258779999919</v>
+        <v>2182.258779999918</v>
       </c>
       <c r="F180">
-        <v>1027.715220054232</v>
+        <v>1027.715220054231</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -7233,10 +7233,10 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>2940.281340565621</v>
+        <v>2940.28134056562</v>
       </c>
       <c r="F181">
-        <v>1027.715220054232</v>
+        <v>1027.715220054231</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="B182">
-        <v>578.3523136292796</v>
+        <v>578.3523136292795</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -7271,10 +7271,10 @@
         <v>1</v>
       </c>
       <c r="E182">
-        <v>2190.670040115109</v>
+        <v>2190.670040115108</v>
       </c>
       <c r="F182">
-        <v>996.7836251957897</v>
+        <v>996.7836251957895</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -7423,10 +7423,10 @@
         <v>1</v>
       </c>
       <c r="E186">
-        <v>2072.00391561835</v>
+        <v>2072.003915618351</v>
       </c>
       <c r="F186">
-        <v>975.7916795243788</v>
+        <v>975.791679524379</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -7461,10 +7461,10 @@
         <v>0</v>
       </c>
       <c r="E187">
-        <v>2791.72869253928</v>
+        <v>2791.728692539281</v>
       </c>
       <c r="F187">
-        <v>975.7916795243789</v>
+        <v>975.791679524379</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>2031.367122745249</v>
       </c>
       <c r="F189">
-        <v>956.6541460143159</v>
+        <v>956.6541460143158</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="B190">
-        <v>752.891688688271</v>
+        <v>752.8916886882711</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -7727,10 +7727,10 @@
         <v>1</v>
       </c>
       <c r="E194">
-        <v>2007.597971723535</v>
+        <v>2007.597971723536</v>
       </c>
       <c r="F194">
-        <v>913.4834308890945</v>
+        <v>913.4834308890946</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         </is>
       </c>
       <c r="B195">
-        <v>558.7915943148763</v>
+        <v>558.7915943148764</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -7765,10 +7765,10 @@
         <v>1</v>
       </c>
       <c r="E195">
-        <v>1939.698078361613</v>
+        <v>1939.698078361614</v>
       </c>
       <c r="F195">
-        <v>913.4834308890945</v>
+        <v>913.4834308890947</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>2613.465514909215</v>
       </c>
       <c r="F196">
-        <v>913.4834308890945</v>
+        <v>913.4834308890946</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="B218">
-        <v>611.7556836339583</v>
+        <v>611.7556836339584</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -8677,10 +8677,10 @@
         <v>1</v>
       </c>
       <c r="E219">
-        <v>1461.48007587693</v>
+        <v>1461.480075876929</v>
       </c>
       <c r="F219">
-        <v>677.8534348501332</v>
+        <v>677.8534348501331</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>1973.210685485709</v>
       </c>
       <c r="F220">
-        <v>677.8534348501332</v>
+        <v>677.8534348501331</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="B221">
-        <v>611.7556836339584</v>
+        <v>611.7556836339583</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -8753,10 +8753,10 @@
         <v>1</v>
       </c>
       <c r="E221">
-        <v>1495.851193686962</v>
+        <v>1495.851193686961</v>
       </c>
       <c r="F221">
-        <v>679.2159543175111</v>
+        <v>679.2159543175109</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         </is>
       </c>
       <c r="B222">
-        <v>598.9003918425917</v>
+        <v>598.9003918425916</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>1464.41772427139</v>
       </c>
       <c r="F222">
-        <v>679.2159543175111</v>
+        <v>679.2159543175109</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="B223">
-        <v>808.6026434649083</v>
+        <v>808.6026434649082</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -8829,10 +8829,10 @@
         <v>0</v>
       </c>
       <c r="E223">
-        <v>1977.176938120848</v>
+        <v>1977.176938120847</v>
       </c>
       <c r="F223">
-        <v>679.2159543175111</v>
+        <v>679.2159543175109</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>1461.48007587693</v>
       </c>
       <c r="F225">
-        <v>677.8534348501333</v>
+        <v>677.8534348501335</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>1973.210685485709</v>
       </c>
       <c r="F226">
-        <v>677.8534348501332</v>
+        <v>677.8534348501333</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="B230">
-        <v>611.7556836339583</v>
+        <v>611.7556836339584</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -9095,10 +9095,10 @@
         <v>1</v>
       </c>
       <c r="E230">
-        <v>1505.903553765304</v>
+        <v>1505.903553765305</v>
       </c>
       <c r="F230">
-        <v>683.7803945322664</v>
+        <v>683.7803945322668</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="B231">
-        <v>598.9003918425917</v>
+        <v>598.9003918425918</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -9133,10 +9133,10 @@
         <v>1</v>
       </c>
       <c r="E231">
-        <v>1474.258846390763</v>
+        <v>1474.258846390764</v>
       </c>
       <c r="F231">
-        <v>683.7803945322665</v>
+        <v>683.7803945322669</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -9171,10 +9171,10 @@
         <v>0</v>
       </c>
       <c r="E232">
-        <v>1990.463884445767</v>
+        <v>1990.463884445768</v>
       </c>
       <c r="F232">
-        <v>683.7803945322665</v>
+        <v>683.7803945322668</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>1513.18268760625</v>
       </c>
       <c r="F240">
-        <v>701.8337774698667</v>
+        <v>701.8337774698666</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>2043.016731846347</v>
       </c>
       <c r="F241">
-        <v>701.8337774698667</v>
+        <v>701.8337774698666</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B242">
-        <v>611.7556836339583</v>
+        <v>611.7556836339584</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>1475.146332630263</v>
       </c>
       <c r="F242">
-        <v>669.8145699946666</v>
+        <v>669.8145699946667</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="B243">
-        <v>598.9003918425917</v>
+        <v>598.9003918425918</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -9589,10 +9589,10 @@
         <v>1</v>
       </c>
       <c r="E243">
-        <v>1444.147950354058</v>
+        <v>1444.147950354059</v>
       </c>
       <c r="F243">
-        <v>669.8145699946666</v>
+        <v>669.8145699946667</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         </is>
       </c>
       <c r="B245">
-        <v>611.7556836339584</v>
+        <v>611.7556836339583</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>1482.948164333559</v>
       </c>
       <c r="F245">
-        <v>673.3571206094222</v>
+        <v>673.3571206094221</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         </is>
       </c>
       <c r="B246">
-        <v>598.9003918425918</v>
+        <v>598.9003918425917</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>1451.785836178736</v>
       </c>
       <c r="F246">
-        <v>673.3571206094223</v>
+        <v>673.3571206094222</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="B247">
-        <v>808.6026434649085</v>
+        <v>808.6026434649082</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -9741,10 +9741,10 @@
         <v>0</v>
       </c>
       <c r="E247">
-        <v>1960.122051794513</v>
+        <v>1960.122051794512</v>
       </c>
       <c r="F247">
-        <v>673.3571206094223</v>
+        <v>673.3571206094219</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         </is>
       </c>
       <c r="B248">
-        <v>611.7556836339584</v>
+        <v>611.7556836339583</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -9779,10 +9779,10 @@
         <v>1</v>
       </c>
       <c r="E248">
-        <v>1486.699044958637</v>
+        <v>1486.699044958638</v>
       </c>
       <c r="F248">
-        <v>675.0602699427554</v>
+        <v>675.0602699427556</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -9817,10 +9817,10 @@
         <v>1</v>
       </c>
       <c r="E249">
-        <v>1455.457896669895</v>
+        <v>1455.457896669896</v>
       </c>
       <c r="F249">
-        <v>675.0602699427556</v>
+        <v>675.0602699427558</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>1965.079867585848</v>
       </c>
       <c r="F250">
-        <v>675.0602699427554</v>
+        <v>675.0602699427556</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -9893,10 +9893,10 @@
         <v>1</v>
       </c>
       <c r="E251">
-        <v>1502.002637913656</v>
+        <v>1502.002637913657</v>
       </c>
       <c r="F251">
-        <v>682.0091192248889</v>
+        <v>682.009119224889</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -9931,10 +9931,10 @@
         <v>1</v>
       </c>
       <c r="E252">
-        <v>1470.439903478424</v>
+        <v>1470.439903478425</v>
       </c>
       <c r="F252">
-        <v>682.0091192248889</v>
+        <v>682.009119224889</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>1985.307756020708</v>
       </c>
       <c r="F253">
-        <v>682.0091192248889</v>
+        <v>682.009119224889</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>1509.804469615386</v>
       </c>
       <c r="F254">
-        <v>685.5516698389333</v>
+        <v>685.5516698389334</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>1478.077789301569</v>
       </c>
       <c r="F255">
-        <v>685.5516698389334</v>
+        <v>685.5516698389335</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -10235,10 +10235,10 @@
         <v>1</v>
       </c>
       <c r="E260">
-        <v>1535.31045787375</v>
+        <v>1535.310457873751</v>
       </c>
       <c r="F260">
-        <v>697.1330853091553</v>
+        <v>697.1330853091555</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         </is>
       </c>
       <c r="B261">
-        <v>598.9003918425917</v>
+        <v>598.9003918425916</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>2029.33316026019</v>
       </c>
       <c r="F262">
-        <v>697.1330853091555</v>
+        <v>697.1330853091556</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>1547.913416777147</v>
       </c>
       <c r="F263">
-        <v>702.8556670705777</v>
+        <v>702.8556670705779</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>1515.385923902479</v>
       </c>
       <c r="F264">
-        <v>702.8556670705777</v>
+        <v>702.8556670705779</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>2045.991421323219</v>
       </c>
       <c r="F265">
-        <v>702.8556670705779</v>
+        <v>702.855667070578</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         </is>
       </c>
       <c r="B269">
-        <v>611.7556836339583</v>
+        <v>611.7556836339584</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>1572.219123233921</v>
       </c>
       <c r="F269">
-        <v>713.8920747534222</v>
+        <v>713.8920747534224</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         </is>
       </c>
       <c r="B270">
-        <v>598.9003918425916</v>
+        <v>598.9003918425918</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>1539.180875891323</v>
       </c>
       <c r="F270">
-        <v>713.8920747534221</v>
+        <v>713.8920747534223</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="B273">
-        <v>598.9003918425918</v>
+        <v>598.9003918425917</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>1541.530994605665</v>
       </c>
       <c r="F273">
-        <v>714.9820903267556</v>
+        <v>714.9820903267555</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         </is>
       </c>
       <c r="B275">
-        <v>611.7556836339584</v>
+        <v>611.7556836339583</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>1569.968594858874</v>
       </c>
       <c r="F275">
-        <v>712.8701851534223</v>
+        <v>712.8701851534222</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         </is>
       </c>
       <c r="B276">
-        <v>598.9003918425917</v>
+        <v>598.9003918425916</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         <v>1</v>
       </c>
       <c r="E276">
-        <v>1536.977639596628</v>
+        <v>1536.977639596627</v>
       </c>
       <c r="F276">
-        <v>712.8701851534222</v>
+        <v>712.8701851534221</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         </is>
       </c>
       <c r="B277">
-        <v>808.6026434649083</v>
+        <v>808.6026434649082</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>2075.143378184553</v>
       </c>
       <c r="F277">
-        <v>712.8701851534223</v>
+        <v>712.8701851534221</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         </is>
       </c>
       <c r="B278">
-        <v>611.7556836339583</v>
+        <v>611.7556836339584</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -10919,10 +10919,10 @@
         <v>1</v>
       </c>
       <c r="E278">
-        <v>1550.313980377197</v>
+        <v>1550.313980377198</v>
       </c>
       <c r="F278">
-        <v>703.9456826439109</v>
+        <v>703.9456826439113</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         </is>
       </c>
       <c r="B279">
-        <v>598.9003918425917</v>
+        <v>598.9003918425918</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -10957,10 +10957,10 @@
         <v>1</v>
       </c>
       <c r="E279">
-        <v>1517.73604261682</v>
+        <v>1517.736042616821</v>
       </c>
       <c r="F279">
-        <v>703.945682643911</v>
+        <v>703.9456826439113</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -10995,10 +10995,10 @@
         <v>0</v>
       </c>
       <c r="E280">
-        <v>2049.164423429673</v>
+        <v>2049.164423429674</v>
       </c>
       <c r="F280">
-        <v>703.945682643911</v>
+        <v>703.9456826439113</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -11033,10 +11033,10 @@
         <v>1</v>
       </c>
       <c r="E281">
-        <v>1544.462606600509</v>
+        <v>1544.462606600508</v>
       </c>
       <c r="F281">
-        <v>701.2887696832</v>
+        <v>701.2887696831999</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="B282">
-        <v>598.9003918425916</v>
+        <v>598.9003918425917</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>1562.466833605584</v>
       </c>
       <c r="F284">
-        <v>709.4638864853334</v>
+        <v>709.4638864853333</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>1529.633518611243</v>
       </c>
       <c r="F285">
-        <v>709.4638864853333</v>
+        <v>709.4638864853332</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         </is>
       </c>
       <c r="B287">
-        <v>611.7556836339583</v>
+        <v>611.7556836339584</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>1577.320320884028</v>
       </c>
       <c r="F287">
-        <v>716.2083578467555</v>
+        <v>716.2083578467558</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         </is>
       </c>
       <c r="B288">
-        <v>598.9003918425917</v>
+        <v>598.9003918425918</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>1544.1748781593</v>
       </c>
       <c r="F288">
-        <v>716.2083578467556</v>
+        <v>716.2083578467558</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         </is>
       </c>
       <c r="B289">
-        <v>808.6026434649083</v>
+        <v>808.6026434649085</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -11337,10 +11337,10 @@
         <v>0</v>
       </c>
       <c r="E289">
-        <v>2084.860697135571</v>
+        <v>2084.860697135572</v>
       </c>
       <c r="F289">
-        <v>716.2083578467555</v>
+        <v>716.2083578467558</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         </is>
       </c>
       <c r="B290">
-        <v>611.7556836339583</v>
+        <v>611.7556836339584</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -11375,10 +11375,10 @@
         <v>1</v>
       </c>
       <c r="E290">
-        <v>1589.923279790556</v>
+        <v>1589.923279790557</v>
       </c>
       <c r="F290">
-        <v>721.9309396095999</v>
+        <v>721.9309396096002</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         </is>
       </c>
       <c r="B291">
-        <v>598.9003918425917</v>
+        <v>598.9003918425918</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>1556.513001415728</v>
       </c>
       <c r="F291">
-        <v>721.9309396096</v>
+        <v>721.9309396096002</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="B292">
-        <v>808.6026434649082</v>
+        <v>808.6026434649085</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -11451,10 +11451,10 @@
         <v>0</v>
       </c>
       <c r="E292">
-        <v>2101.518958202739</v>
+        <v>2101.51895820274</v>
       </c>
       <c r="F292">
-        <v>721.9309396095998</v>
+        <v>721.9309396096002</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="B297">
-        <v>598.9003918425916</v>
+        <v>598.9003918425917</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>2081.489382397463</v>
       </c>
       <c r="F298">
-        <v>715.0502163000891</v>
+        <v>715.0502163000889</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         </is>
       </c>
       <c r="B299">
-        <v>611.7556836339584</v>
+        <v>611.7556836339583</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -11717,10 +11717,10 @@
         <v>1</v>
       </c>
       <c r="E299">
-        <v>1589.923279790557</v>
+        <v>1589.923279790556</v>
       </c>
       <c r="F299">
-        <v>721.9309396096002</v>
+        <v>721.9309396096</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         </is>
       </c>
       <c r="B301">
-        <v>808.6026434649083</v>
+        <v>808.6026434649082</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -11793,10 +11793,10 @@
         <v>0</v>
       </c>
       <c r="E301">
-        <v>2101.51895820274</v>
+        <v>2101.518958202739</v>
       </c>
       <c r="F301">
-        <v>721.9309396096</v>
+        <v>721.9309396095998</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         </is>
       </c>
       <c r="B344">
-        <v>611.7556836339583</v>
+        <v>611.7556836339584</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -13427,10 +13427,10 @@
         <v>1</v>
       </c>
       <c r="E344">
-        <v>1953.008524395261</v>
+        <v>1953.008524395262</v>
       </c>
       <c r="F344">
-        <v>886.7957951203554</v>
+        <v>886.7957951203556</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         </is>
       </c>
       <c r="B345">
-        <v>598.9003918425917</v>
+        <v>598.9003918425918</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>2041.379271947171</v>
       </c>
       <c r="F347">
-        <v>926.9219934250666</v>
+        <v>926.9219934250664</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
       <c r="B348">
-        <v>598.9003918425917</v>
+        <v>598.9003918425916</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>1998.482202251239</v>
       </c>
       <c r="F348">
-        <v>926.9219934250666</v>
+        <v>926.9219934250665</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         </is>
       </c>
       <c r="B349">
-        <v>808.6026434649083</v>
+        <v>808.6026434649082</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -13617,10 +13617,10 @@
         <v>0</v>
       </c>
       <c r="E349">
-        <v>2698.241667009377</v>
+        <v>2698.241667009376</v>
       </c>
       <c r="F349">
-        <v>926.9219934250666</v>
+        <v>926.9219934250664</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         </is>
       </c>
       <c r="B351">
-        <v>598.9003918425917</v>
+        <v>598.9003918425918</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>2137.286088853854</v>
       </c>
       <c r="F351">
-        <v>991.3010382421334</v>
+        <v>991.3010382421336</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         </is>
       </c>
       <c r="B352">
-        <v>808.6026434649083</v>
+        <v>808.6026434649085</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -13731,10 +13731,10 @@
         <v>0</v>
       </c>
       <c r="E352">
-        <v>2885.64710397155</v>
+        <v>2885.647103971551</v>
       </c>
       <c r="F352">
-        <v>991.3010382421334</v>
+        <v>991.3010382421336</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>1</v>
       </c>
       <c r="E356">
-        <v>2293.588485243232</v>
+        <v>2293.588485243231</v>
       </c>
       <c r="F356">
         <v>1041.441754628267</v>
@@ -13910,7 +13910,7 @@
         </is>
       </c>
       <c r="B357">
-        <v>598.9003918425918</v>
+        <v>598.9003918425917</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -13921,10 +13921,10 @@
         <v>1</v>
       </c>
       <c r="E357">
-        <v>2245.391549741179</v>
+        <v>2245.391549741178</v>
       </c>
       <c r="F357">
-        <v>1041.441754628267</v>
+        <v>1041.441754628266</v>
       </c>
       <c r="G357" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="B358">
-        <v>808.6026434649085</v>
+        <v>808.6026434649083</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>0</v>
       </c>
       <c r="E358">
-        <v>3031.605200905737</v>
+        <v>3031.605200905736</v>
       </c>
       <c r="F358">
         <v>1041.441754628267</v>
@@ -13997,7 +13997,7 @@
         <v>1</v>
       </c>
       <c r="E359">
-        <v>2357.053385438354</v>
+        <v>2357.053385438355</v>
       </c>
       <c r="F359">
         <v>1070.2590413568</v>
@@ -14035,7 +14035,7 @@
         <v>1</v>
       </c>
       <c r="E360">
-        <v>2307.52281326999</v>
+        <v>2307.522813269991</v>
       </c>
       <c r="F360">
         <v>1070.2590413568</v>
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="B362">
-        <v>611.7556836339584</v>
+        <v>611.7556836339583</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>1</v>
       </c>
       <c r="E363">
-        <v>2346.74041932477</v>
+        <v>2346.740419324771</v>
       </c>
       <c r="F363">
         <v>1088.448676241067</v>
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="B368">
-        <v>611.7556836339583</v>
+        <v>611.7556836339584</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -14339,10 +14339,10 @@
         <v>1</v>
       </c>
       <c r="E368">
-        <v>2468.379522422008</v>
+        <v>2468.379522422009</v>
       </c>
       <c r="F368">
-        <v>1120.808513584355</v>
+        <v>1120.808513584356</v>
       </c>
       <c r="G368" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         </is>
       </c>
       <c r="B369">
-        <v>598.9003918425917</v>
+        <v>598.9003918425918</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -14377,10 +14377,10 @@
         <v>1</v>
       </c>
       <c r="E369">
-        <v>2416.509568678259</v>
+        <v>2416.50956867826</v>
       </c>
       <c r="F369">
-        <v>1120.808513584355</v>
+        <v>1120.808513584356</v>
       </c>
       <c r="G369" t="inlineStr">
         <is>
@@ -14415,10 +14415,10 @@
         <v>0</v>
       </c>
       <c r="E370">
-        <v>3262.639416848223</v>
+        <v>3262.639416848224</v>
       </c>
       <c r="F370">
-        <v>1120.808513584355</v>
+        <v>1120.808513584356</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         </is>
       </c>
       <c r="B374">
-        <v>611.7556836339583</v>
+        <v>611.7556836339584</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         </is>
       </c>
       <c r="B375">
-        <v>598.9003918425917</v>
+        <v>598.9003918425918</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>0</v>
       </c>
       <c r="E379">
-        <v>3261.647853685817</v>
+        <v>3261.647853685818</v>
       </c>
       <c r="F379">
         <v>1120.467883716267</v>
@@ -14784,7 +14784,7 @@
         </is>
       </c>
       <c r="B380">
-        <v>579.5580160742762</v>
+        <v>579.5580160742763</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         </is>
       </c>
       <c r="B381">
-        <v>567.3793185877183</v>
+        <v>567.3793185877186</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>0</v>
       </c>
       <c r="E382">
-        <v>3189.417227755773</v>
+        <v>3189.417227755772</v>
       </c>
       <c r="F382">
         <v>1095.654629739789</v>
@@ -14898,7 +14898,7 @@
         </is>
       </c>
       <c r="B383">
-        <v>579.5580160742761</v>
+        <v>579.5580160742762</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         </is>
       </c>
       <c r="B384">
-        <v>567.3793185877183</v>
+        <v>567.3793185877184</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         </is>
       </c>
       <c r="B389">
-        <v>579.5580160742762</v>
+        <v>579.5580160742763</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         </is>
       </c>
       <c r="B399">
-        <v>567.3793185877184</v>
+        <v>567.3793185877183</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
@@ -15517,10 +15517,10 @@
         <v>1</v>
       </c>
       <c r="E399">
-        <v>2035.024458221944</v>
+        <v>2035.024458221943</v>
       </c>
       <c r="F399">
-        <v>943.8707662039579</v>
+        <v>943.8707662039577</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>2747.579027910368</v>
       </c>
       <c r="F400">
-        <v>943.8707662039581</v>
+        <v>943.8707662039578</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
@@ -15593,10 +15593,10 @@
         <v>1</v>
       </c>
       <c r="E401">
-        <v>2033.516642309705</v>
+        <v>2033.516642309704</v>
       </c>
       <c r="F401">
-        <v>923.3518365035791</v>
+        <v>923.3518365035789</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         </is>
       </c>
       <c r="B402">
-        <v>567.3793185877186</v>
+        <v>567.3793185877184</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
@@ -15631,10 +15631,10 @@
         <v>1</v>
       </c>
       <c r="E402">
-        <v>1990.784796086053</v>
+        <v>1990.784796086052</v>
       </c>
       <c r="F402">
-        <v>923.3518365035792</v>
+        <v>923.3518365035789</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
@@ -15669,10 +15669,10 @@
         <v>0</v>
       </c>
       <c r="E403">
-        <v>2687.849049041899</v>
+        <v>2687.849049041898</v>
       </c>
       <c r="F403">
-        <v>923.3518365035791</v>
+        <v>923.3518365035789</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         </is>
       </c>
       <c r="B405">
-        <v>567.3793185877184</v>
+        <v>567.3793185877186</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
@@ -15745,10 +15745,10 @@
         <v>1</v>
       </c>
       <c r="E405">
-        <v>1957.756555179663</v>
+        <v>1957.756555179664</v>
       </c>
       <c r="F405">
-        <v>908.0329095370106</v>
+        <v>908.0329095370107</v>
       </c>
       <c r="G405" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         </is>
       </c>
       <c r="B406">
-        <v>766.0446095983342</v>
+        <v>766.0446095983343</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
@@ -15783,10 +15783,10 @@
         <v>0</v>
       </c>
       <c r="E406">
-        <v>2643.256119617131</v>
+        <v>2643.256119617132</v>
       </c>
       <c r="F406">
-        <v>908.0329095370105</v>
+        <v>908.0329095370108</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         </is>
       </c>
       <c r="B407">
-        <v>579.5580160742765</v>
+        <v>579.5580160742763</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
@@ -15821,10 +15821,10 @@
         <v>1</v>
       </c>
       <c r="E407">
-        <v>1951.649800318674</v>
+        <v>1951.649800318673</v>
       </c>
       <c r="F407">
-        <v>886.1788439996633</v>
+        <v>886.1788439996631</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         </is>
       </c>
       <c r="B414">
-        <v>567.3793185877186</v>
+        <v>567.3793185877184</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>1840.794160767147</v>
       </c>
       <c r="F414">
-        <v>853.7842323846738</v>
+        <v>853.7842323846737</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>2485.339874117657</v>
       </c>
       <c r="F415">
-        <v>853.7842323846738</v>
+        <v>853.7842323846737</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         </is>
       </c>
       <c r="B416">
-        <v>579.5580160742763</v>
+        <v>579.5580160742762</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="B417">
-        <v>567.3793185877183</v>
+        <v>567.3793185877184</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
@@ -16201,10 +16201,10 @@
         <v>1</v>
       </c>
       <c r="E417">
-        <v>1806.856885703559</v>
+        <v>1806.85688570356</v>
       </c>
       <c r="F417">
-        <v>838.0436835732208</v>
+        <v>838.0436835732212</v>
       </c>
       <c r="G417" t="inlineStr">
         <is>
@@ -16239,10 +16239,10 @@
         <v>0</v>
       </c>
       <c r="E418">
-        <v>2439.519616354952</v>
+        <v>2439.519616354953</v>
       </c>
       <c r="F418">
-        <v>838.0436835732208</v>
+        <v>838.0436835732212</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         </is>
       </c>
       <c r="B419">
-        <v>579.5580160742763</v>
+        <v>579.5580160742765</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>1839.759957669884</v>
       </c>
       <c r="F419">
-        <v>835.3734118992843</v>
+        <v>835.3734118992842</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="B420">
-        <v>567.3793185877184</v>
+        <v>567.3793185877186</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         </is>
       </c>
       <c r="B421">
-        <v>766.0446095983342</v>
+        <v>766.0446095983343</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         </is>
       </c>
       <c r="B422">
-        <v>579.5580160742765</v>
+        <v>579.5580160742763</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
@@ -16391,10 +16391,10 @@
         <v>1</v>
       </c>
       <c r="E422">
-        <v>1825.367488285385</v>
+        <v>1825.367488285384</v>
       </c>
       <c r="F422">
-        <v>828.8382733312001</v>
+        <v>828.8382733312</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>1820.569998490551</v>
       </c>
       <c r="F425">
-        <v>826.6598938085051</v>
+        <v>826.6598938085053</v>
       </c>
       <c r="G425" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>1782.312963560888</v>
       </c>
       <c r="F426">
-        <v>826.6598938085051</v>
+        <v>826.6598938085052</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
@@ -16619,10 +16619,10 @@
         <v>1</v>
       </c>
       <c r="E428">
-        <v>1820.260483017619</v>
+        <v>1820.26048301762</v>
       </c>
       <c r="F428">
-        <v>826.5193531930947</v>
+        <v>826.519353193095</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         </is>
       </c>
       <c r="B429">
-        <v>567.3793185877184</v>
+        <v>567.3793185877183</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         </is>
       </c>
       <c r="B430">
-        <v>766.0446095983342</v>
+        <v>766.0446095983341</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
@@ -16695,10 +16695,10 @@
         <v>0</v>
       </c>
       <c r="E430">
-        <v>2405.972641920633</v>
+        <v>2405.972641920634</v>
       </c>
       <c r="F430">
-        <v>826.5193531930946</v>
+        <v>826.5193531930947</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         </is>
       </c>
       <c r="B431">
-        <v>579.5580160742763</v>
+        <v>579.5580160742765</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>1822.736606783269</v>
       </c>
       <c r="F431">
-        <v>827.6436781082947</v>
+        <v>827.6436781082949</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
@@ -16771,10 +16771,10 @@
         <v>1</v>
       </c>
       <c r="E432">
-        <v>1784.434043250365</v>
+        <v>1784.434043250366</v>
       </c>
       <c r="F432">
-        <v>827.6436781082946</v>
+        <v>827.6436781082948</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
@@ -16809,10 +16809,10 @@
         <v>0</v>
       </c>
       <c r="E433">
-        <v>2409.245517475392</v>
+        <v>2409.245517475393</v>
       </c>
       <c r="F433">
-        <v>827.6436781082947</v>
+        <v>827.6436781082949</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
@@ -16847,10 +16847,10 @@
         <v>1</v>
       </c>
       <c r="E434">
-        <v>1541.673687780468</v>
+        <v>1541.673687780469</v>
       </c>
       <c r="F434">
-        <v>700.4905761016888</v>
+        <v>700.4905761016889</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         </is>
       </c>
       <c r="B435">
-        <v>590.5200566430029</v>
+        <v>590.5200566430028</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
@@ -16885,10 +16885,10 @@
         <v>1</v>
       </c>
       <c r="E435">
-        <v>1489.153444838853</v>
+        <v>1489.153444838852</v>
       </c>
       <c r="F435">
-        <v>700.490576101689</v>
+        <v>700.4905761016889</v>
       </c>
       <c r="G435" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         </is>
       </c>
       <c r="B436">
-        <v>747.3635827251778</v>
+        <v>747.3635827251776</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         </is>
       </c>
       <c r="B438">
-        <v>590.5200566430028</v>
+        <v>590.5200566430029</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>1495.680265396289</v>
       </c>
       <c r="F438">
-        <v>703.560760915911</v>
+        <v>703.5607609159111</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         </is>
       </c>
       <c r="B440">
-        <v>611.3468270099368</v>
+        <v>611.3468270099366</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>1544.130783009786</v>
       </c>
       <c r="F440">
-        <v>701.607006943289</v>
+        <v>701.6070069432888</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         </is>
       </c>
       <c r="B441">
-        <v>590.5200566430029</v>
+        <v>590.5200566430028</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>1491.526834132603</v>
       </c>
       <c r="F441">
-        <v>701.607006943289</v>
+        <v>701.6070069432889</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         </is>
       </c>
       <c r="B442">
-        <v>747.3635827251779</v>
+        <v>747.3635827251778</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>1887.67989494721</v>
       </c>
       <c r="F442">
-        <v>701.607006943289</v>
+        <v>701.6070069432889</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         </is>
       </c>
       <c r="B443">
-        <v>611.3468270099368</v>
+        <v>611.3468270099366</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
@@ -17189,10 +17189,10 @@
         <v>1</v>
       </c>
       <c r="E443">
-        <v>1587.590654872373</v>
+        <v>1587.590654872372</v>
       </c>
       <c r="F443">
-        <v>721.353877451378</v>
+        <v>721.3538774513777</v>
       </c>
       <c r="G443" t="inlineStr">
         <is>
@@ -17227,10 +17227,10 @@
         <v>1</v>
       </c>
       <c r="E444">
-        <v>1533.506157260055</v>
+        <v>1533.506157260054</v>
       </c>
       <c r="F444">
-        <v>721.3538774513779</v>
+        <v>721.3538774513778</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         </is>
       </c>
       <c r="B445">
-        <v>747.3635827251778</v>
+        <v>747.3635827251776</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
@@ -17265,10 +17265,10 @@
         <v>0</v>
       </c>
       <c r="E445">
-        <v>1940.809025753138</v>
+        <v>1940.809025753137</v>
       </c>
       <c r="F445">
-        <v>721.3538774513779</v>
+        <v>721.3538774513776</v>
       </c>
       <c r="G445" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         </is>
       </c>
       <c r="B447">
-        <v>590.5200566430028</v>
+        <v>590.5200566430029</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>1534.247841414068</v>
       </c>
       <c r="F447">
-        <v>721.7027620892443</v>
+        <v>721.7027620892444</v>
       </c>
       <c r="G447" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         </is>
       </c>
       <c r="B448">
-        <v>747.3635827251779</v>
+        <v>747.3635827251778</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>1941.747702975628</v>
       </c>
       <c r="F448">
-        <v>721.7027620892445</v>
+        <v>721.7027620892444</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         </is>
       </c>
       <c r="B451">
-        <v>747.3635827251777</v>
+        <v>747.3635827251778</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>1959.582570210585</v>
       </c>
       <c r="F451">
-        <v>728.3315702115555</v>
+        <v>728.3315702115556</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         </is>
       </c>
       <c r="B455">
-        <v>579.1706782199401</v>
+        <v>579.17067821994</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
@@ -17645,10 +17645,10 @@
         <v>1</v>
       </c>
       <c r="E455">
-        <v>1603.778256209891</v>
+        <v>1603.77825620989</v>
       </c>
       <c r="F455">
-        <v>728.7090410482529</v>
+        <v>728.7090410482524</v>
       </c>
       <c r="G455" t="inlineStr">
         <is>
@@ -17683,10 +17683,10 @@
         <v>1</v>
       </c>
       <c r="E456">
-        <v>1549.142295105897</v>
+        <v>1549.142295105896</v>
       </c>
       <c r="F456">
-        <v>728.7090410482527</v>
+        <v>728.7090410482525</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="B457">
-        <v>708.0286573185895</v>
+        <v>708.0286573185894</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="E457">
-        <v>1960.598158855383</v>
+        <v>1960.598158855382</v>
       </c>
       <c r="F457">
-        <v>728.7090410482527</v>
+        <v>728.7090410482524</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         </is>
       </c>
       <c r="B459">
-        <v>590.5200566430029</v>
+        <v>590.5200566430028</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>1521.194200302219</v>
       </c>
       <c r="F459">
-        <v>715.5623924622223</v>
+        <v>715.5623924622222</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         </is>
       </c>
       <c r="B460">
-        <v>747.3635827251778</v>
+        <v>747.3635827251777</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>1925.226983858278</v>
       </c>
       <c r="F460">
-        <v>715.5623924622222</v>
+        <v>715.5623924622221</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         </is>
       </c>
       <c r="B461">
-        <v>611.3468270099366</v>
+        <v>611.3468270099368</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>1571.158830530713</v>
       </c>
       <c r="F461">
-        <v>713.8877462001777</v>
+        <v>713.8877462001778</v>
       </c>
       <c r="G461" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         </is>
       </c>
       <c r="B462">
-        <v>590.5200566430028</v>
+        <v>590.5200566430029</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>1517.634116362349</v>
       </c>
       <c r="F462">
-        <v>713.8877462001778</v>
+        <v>713.887746200178</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         </is>
       </c>
       <c r="B463">
-        <v>747.3635827251777</v>
+        <v>747.3635827251779</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
@@ -17949,10 +17949,10 @@
         <v>0</v>
       </c>
       <c r="E463">
-        <v>1920.721333189562</v>
+        <v>1920.721333189563</v>
       </c>
       <c r="F463">
-        <v>713.8877462001777</v>
+        <v>713.887746200178</v>
       </c>
       <c r="G463" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         </is>
       </c>
       <c r="B464">
-        <v>611.3468270099368</v>
+        <v>611.3468270099366</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
@@ -17987,10 +17987,10 @@
         <v>1</v>
       </c>
       <c r="E464">
-        <v>1562.098291872312</v>
+        <v>1562.098291872311</v>
       </c>
       <c r="F464">
-        <v>709.7709074716445</v>
+        <v>709.7709074716443</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         </is>
       </c>
       <c r="B465">
-        <v>590.5200566430029</v>
+        <v>590.5200566430027</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
@@ -18025,10 +18025,10 @@
         <v>1</v>
       </c>
       <c r="E465">
-        <v>1508.88224334136</v>
+        <v>1508.882243341359</v>
       </c>
       <c r="F465">
-        <v>709.7709074716445</v>
+        <v>709.7709074716441</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         </is>
       </c>
       <c r="B466">
-        <v>747.3635827251779</v>
+        <v>747.3635827251776</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
@@ -18063,10 +18063,10 @@
         <v>0</v>
       </c>
       <c r="E466">
-        <v>1909.644941959592</v>
+        <v>1909.644941959591</v>
       </c>
       <c r="F466">
-        <v>709.7709074716445</v>
+        <v>709.7709074716441</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         </is>
       </c>
       <c r="B468">
-        <v>590.5200566430028</v>
+        <v>590.5200566430029</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>1509.475590665175</v>
       </c>
       <c r="F468">
-        <v>710.0500151822222</v>
+        <v>710.0500151822223</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         </is>
       </c>
       <c r="B470">
-        <v>611.3468270099366</v>
+        <v>611.3468270099368</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         </is>
       </c>
       <c r="B471">
-        <v>590.5200566430028</v>
+        <v>590.5200566430029</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         </is>
       </c>
       <c r="B472">
-        <v>747.3635827251778</v>
+        <v>747.3635827251779</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         </is>
       </c>
       <c r="B473">
-        <v>611.3468270099366</v>
+        <v>611.3468270099368</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
@@ -18329,10 +18329,10 @@
         <v>1</v>
       </c>
       <c r="E473">
-        <v>1564.248250197768</v>
+        <v>1564.248250197769</v>
       </c>
       <c r="F473">
-        <v>710.7477844579554</v>
+        <v>710.7477844579555</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         </is>
       </c>
       <c r="B475">
-        <v>747.3635827251777</v>
+        <v>747.3635827251779</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>1912.273238183328</v>
       </c>
       <c r="F475">
-        <v>710.7477844579553</v>
+        <v>710.7477844579555</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>1583.290738221458</v>
       </c>
       <c r="F476">
-        <v>719.4001234787557</v>
+        <v>719.4001234787555</v>
       </c>
       <c r="G476" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         </is>
       </c>
       <c r="B477">
-        <v>590.5200566430029</v>
+        <v>590.5200566430028</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
@@ -18481,10 +18481,10 @@
         <v>1</v>
       </c>
       <c r="E477">
-        <v>1529.352725996369</v>
+        <v>1529.352725996368</v>
       </c>
       <c r="F477">
-        <v>719.4001234787559</v>
+        <v>719.4001234787554</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         </is>
       </c>
       <c r="B478">
-        <v>747.3635827251778</v>
+        <v>747.3635827251779</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>1935.552433305665</v>
       </c>
       <c r="F478">
-        <v>719.4001234787556</v>
+        <v>719.4001234787555</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         </is>
       </c>
       <c r="B481">
-        <v>747.3635827251778</v>
+        <v>747.3635827251777</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>1963.149543656811</v>
       </c>
       <c r="F481">
-        <v>729.6573318357333</v>
+        <v>729.6573318357332</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         </is>
       </c>
       <c r="B482">
-        <v>611.3468270099366</v>
+        <v>611.3468270099368</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>1601.104678632836</v>
       </c>
       <c r="F482">
-        <v>727.4942470798221</v>
+        <v>727.494247079822</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="B483">
-        <v>590.5200566430028</v>
+        <v>590.5200566430029</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>1546.559798374927</v>
       </c>
       <c r="F483">
-        <v>727.4942470798221</v>
+        <v>727.494247079822</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         </is>
       </c>
       <c r="B484">
-        <v>747.3635827251778</v>
+        <v>747.3635827251779</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>1957.329744874314</v>
       </c>
       <c r="F484">
-        <v>727.4942470798221</v>
+        <v>727.494247079822</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         </is>
       </c>
       <c r="B485">
-        <v>611.3468270099368</v>
+        <v>611.3468270099366</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>1</v>
       </c>
       <c r="E485">
-        <v>1608.936669675797</v>
+        <v>1608.936669675796</v>
       </c>
       <c r="F485">
         <v>731.0528703872</v>
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="B486">
-        <v>590.5200566430029</v>
+        <v>590.5200566430028</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>1610.472354193533</v>
       </c>
       <c r="F488">
-        <v>731.7506396629333</v>
+        <v>731.7506396629334</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         </is>
       </c>
       <c r="B489">
-        <v>590.5200566430029</v>
+        <v>590.5200566430028</v>
       </c>
       <c r="C489" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="B490">
-        <v>747.3635827251777</v>
+        <v>747.3635827251778</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
@@ -18975,10 +18975,10 @@
         <v>0</v>
       </c>
       <c r="E490">
-        <v>1968.781606991749</v>
+        <v>1968.78160699175</v>
       </c>
       <c r="F490">
-        <v>731.7506396629332</v>
+        <v>731.7506396629334</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         </is>
       </c>
       <c r="B491">
-        <v>611.3468270099368</v>
+        <v>611.3468270099366</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>1589.126339390109</v>
       </c>
       <c r="F491">
-        <v>722.0516467271112</v>
+        <v>722.0516467271111</v>
       </c>
       <c r="G491" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         </is>
       </c>
       <c r="B492">
-        <v>590.5200566430029</v>
+        <v>590.5200566430028</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
@@ -19051,10 +19051,10 @@
         <v>1</v>
       </c>
       <c r="E492">
-        <v>1534.989525568082</v>
+        <v>1534.989525568081</v>
       </c>
       <c r="F492">
-        <v>722.0516467271113</v>
+        <v>722.0516467271111</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="B493">
-        <v>747.3635827251779</v>
+        <v>747.3635827251778</v>
       </c>
       <c r="C493" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>1942.686380198117</v>
       </c>
       <c r="F493">
-        <v>722.0516467271111</v>
+        <v>722.051646727111</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         </is>
       </c>
       <c r="B494">
-        <v>611.3468270099366</v>
+        <v>611.3468270099368</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>1582.062190609147</v>
       </c>
       <c r="F494">
-        <v>718.8419080590221</v>
+        <v>718.8419080590224</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         </is>
       </c>
       <c r="B495">
-        <v>590.5200566430028</v>
+        <v>590.5200566430029</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
@@ -19165,10 +19165,10 @@
         <v>1</v>
       </c>
       <c r="E495">
-        <v>1528.166031351761</v>
+        <v>1528.166031351762</v>
       </c>
       <c r="F495">
-        <v>718.8419080590222</v>
+        <v>718.8419080590226</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>1934.050549751978</v>
       </c>
       <c r="F496">
-        <v>718.8419080590222</v>
+        <v>718.8419080590224</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         </is>
       </c>
       <c r="B497">
-        <v>611.3468270099366</v>
+        <v>611.3468270099368</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>1573.923062660761</v>
       </c>
       <c r="F497">
-        <v>715.1437308956445</v>
+        <v>715.1437308956444</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
@@ -19279,10 +19279,10 @@
         <v>1</v>
       </c>
       <c r="E498">
-        <v>1520.304179314984</v>
+        <v>1520.304179314983</v>
       </c>
       <c r="F498">
-        <v>715.1437308956446</v>
+        <v>715.1437308956445</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>1924.100571188229</v>
       </c>
       <c r="F499">
-        <v>715.1437308956446</v>
+        <v>715.1437308956444</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>1588.665634036666</v>
       </c>
       <c r="F500">
-        <v>721.8423159452443</v>
+        <v>721.8423159452444</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         </is>
       </c>
       <c r="B507">
-        <v>590.5200566430028</v>
+        <v>590.5200566430029</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>1533.951167753672</v>
       </c>
       <c r="F507">
-        <v>721.5632082346666</v>
+        <v>721.5632082346667</v>
       </c>
       <c r="G507" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         </is>
       </c>
       <c r="B510">
-        <v>590.5200566430028</v>
+        <v>590.5200566430029</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         </is>
       </c>
       <c r="B511">
-        <v>747.3635827251778</v>
+        <v>747.3635827251779</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
@@ -19773,10 +19773,10 @@
         <v>0</v>
       </c>
       <c r="E511">
-        <v>1965.214633545524</v>
+        <v>1965.214633545523</v>
       </c>
       <c r="F511">
-        <v>730.4248780387557</v>
+        <v>730.4248780387555</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
@@ -19814,7 +19814,7 @@
         <v>1608.01525896578</v>
       </c>
       <c r="F512">
-        <v>730.6342088220443</v>
+        <v>730.6342088220442</v>
       </c>
       <c r="G512" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         </is>
       </c>
       <c r="B513">
-        <v>590.5200566430029</v>
+        <v>590.5200566430028</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>1553.234955764073</v>
       </c>
       <c r="F513">
-        <v>730.6342088220445</v>
+        <v>730.6342088220443</v>
       </c>
       <c r="G513" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         </is>
       </c>
       <c r="B514">
-        <v>747.3635827251778</v>
+        <v>747.3635827251776</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
@@ -19887,10 +19887,10 @@
         <v>0</v>
       </c>
       <c r="E514">
-        <v>1965.777839880548</v>
+        <v>1965.777839880547</v>
       </c>
       <c r="F514">
-        <v>730.6342088220443</v>
+        <v>730.6342088220442</v>
       </c>
       <c r="G514" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         </is>
       </c>
       <c r="B515">
-        <v>611.3468270099366</v>
+        <v>611.3468270099368</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>1624.293514856292</v>
       </c>
       <c r="F515">
-        <v>738.0305631459554</v>
+        <v>738.0305631459556</v>
       </c>
       <c r="G515" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         </is>
       </c>
       <c r="B516">
-        <v>590.5200566430028</v>
+        <v>590.5200566430029</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>1568.958659831581</v>
       </c>
       <c r="F516">
-        <v>738.0305631459555</v>
+        <v>738.0305631459556</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         </is>
       </c>
       <c r="B517">
-        <v>747.3635827251777</v>
+        <v>747.3635827251779</v>
       </c>
       <c r="C517" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>1985.677797000391</v>
       </c>
       <c r="F517">
-        <v>738.0305631459555</v>
+        <v>738.0305631459556</v>
       </c>
       <c r="G517" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         </is>
       </c>
       <c r="B521">
-        <v>611.3468270099366</v>
+        <v>611.3468270099368</v>
       </c>
       <c r="C521" t="inlineStr">
         <is>
@@ -20153,10 +20153,10 @@
         <v>1</v>
       </c>
       <c r="E521">
-        <v>1649.478740954057</v>
+        <v>1649.478740954058</v>
       </c>
       <c r="F521">
-        <v>749.4739792711111</v>
+        <v>749.4739792711113</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         </is>
       </c>
       <c r="B522">
-        <v>590.5200566430027</v>
+        <v>590.5200566430029</v>
       </c>
       <c r="C522" t="inlineStr">
         <is>
@@ -20191,10 +20191,10 @@
         <v>1</v>
       </c>
       <c r="E522">
-        <v>1593.285900089879</v>
+        <v>1593.28590008988</v>
       </c>
       <c r="F522">
-        <v>749.4739792711109</v>
+        <v>749.4739792711111</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         </is>
       </c>
       <c r="B523">
-        <v>747.3635827251777</v>
+        <v>747.3635827251778</v>
       </c>
       <c r="C523" t="inlineStr">
         <is>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="E523">
-        <v>2016.466409906471</v>
+        <v>2016.466409906472</v>
       </c>
       <c r="F523">
-        <v>749.473979271111</v>
+        <v>749.4739792711111</v>
       </c>
       <c r="G523" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         </is>
       </c>
       <c r="B524">
-        <v>611.3468270099368</v>
+        <v>611.3468270099366</v>
       </c>
       <c r="C524" t="inlineStr">
         <is>
@@ -20267,10 +20267,10 @@
         <v>1</v>
       </c>
       <c r="E524">
-        <v>1682.649526549062</v>
+        <v>1682.649526549061</v>
       </c>
       <c r="F524">
-        <v>764.5457956323559</v>
+        <v>764.5457956323556</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         </is>
       </c>
       <c r="B525">
-        <v>590.5200566430029</v>
+        <v>590.5200566430028</v>
       </c>
       <c r="C525" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>1625.326655554758</v>
       </c>
       <c r="F525">
-        <v>764.5457956323559</v>
+        <v>764.5457956323556</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         </is>
       </c>
       <c r="B526">
-        <v>747.3635827251779</v>
+        <v>747.3635827251778</v>
       </c>
       <c r="C526" t="inlineStr">
         <is>
@@ -20343,10 +20343,10 @@
         <v>0</v>
       </c>
       <c r="E526">
-        <v>2057.017265932569</v>
+        <v>2057.017265932568</v>
       </c>
       <c r="F526">
-        <v>764.5457956323559</v>
+        <v>764.5457956323557</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>1707.834752646826</v>
       </c>
       <c r="F527">
-        <v>775.9892117575109</v>
+        <v>775.989211757511</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         </is>
       </c>
       <c r="B529">
-        <v>747.3635827251777</v>
+        <v>747.3635827251778</v>
       </c>
       <c r="C529" t="inlineStr">
         <is>
@@ -20495,10 +20495,10 @@
         <v>1</v>
       </c>
       <c r="E530">
-        <v>1718.277407368688</v>
+        <v>1718.277407368687</v>
       </c>
       <c r="F530">
-        <v>780.734042833067</v>
+        <v>780.7340428330668</v>
       </c>
       <c r="G530" t="inlineStr">
         <is>
@@ -20533,10 +20533,10 @@
         <v>1</v>
       </c>
       <c r="E531">
-        <v>1659.740800308852</v>
+        <v>1659.740800308851</v>
       </c>
       <c r="F531">
-        <v>780.734042833067</v>
+        <v>780.7340428330667</v>
       </c>
       <c r="G531" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>2100.57188906604</v>
       </c>
       <c r="F532">
-        <v>780.7340428330671</v>
+        <v>780.7340428330668</v>
       </c>
       <c r="G532" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>1722.423755568454</v>
       </c>
       <c r="F533">
-        <v>782.6180198784002</v>
+        <v>782.6180198783999</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         </is>
       </c>
       <c r="B534">
-        <v>590.5200566430029</v>
+        <v>590.5200566430028</v>
       </c>
       <c r="C534" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>1663.745894742339</v>
       </c>
       <c r="F534">
-        <v>782.6180198784003</v>
+        <v>782.6180198784</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         </is>
       </c>
       <c r="B535">
-        <v>747.3635827251779</v>
+        <v>747.3635827251777</v>
       </c>
       <c r="C535" t="inlineStr">
         <is>
@@ -20685,10 +20685,10 @@
         <v>0</v>
       </c>
       <c r="E535">
-        <v>2105.64074606978</v>
+        <v>2105.640746069779</v>
       </c>
       <c r="F535">
-        <v>782.6180198784002</v>
+        <v>782.6180198783999</v>
       </c>
       <c r="G535" t="inlineStr">
         <is>
@@ -20723,10 +20723,10 @@
         <v>1</v>
       </c>
       <c r="E536">
-        <v>1736.989106798109</v>
+        <v>1740.895902383341</v>
       </c>
       <c r="F536">
-        <v>789.2360813753655</v>
+        <v>791.0112128522153</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         </is>
       </c>
       <c r="B537">
-        <v>602.2300860948471</v>
+        <v>602.230086094847</v>
       </c>
       <c r="C537" t="inlineStr">
         <is>
@@ -20761,10 +20761,10 @@
         <v>1</v>
       </c>
       <c r="E537">
-        <v>1677.815047722537</v>
+        <v>1681.588750387466</v>
       </c>
       <c r="F537">
-        <v>789.2360813753655</v>
+        <v>791.0112128522151</v>
       </c>
       <c r="G537" t="inlineStr">
         <is>
@@ -20799,10 +20799,10 @@
         <v>0</v>
       </c>
       <c r="E538">
-        <v>2123.446699413623</v>
+        <v>2128.222706446871</v>
       </c>
       <c r="F538">
-        <v>789.2360813753655</v>
+        <v>791.0112128522152</v>
       </c>
       <c r="G538" t="inlineStr">
         <is>
@@ -20837,10 +20837,10 @@
         <v>1</v>
       </c>
       <c r="E539">
-        <v>1757.395269040215</v>
+        <v>1760.994431964327</v>
       </c>
       <c r="F539">
-        <v>798.508033318436</v>
+        <v>800.1433856826741</v>
       </c>
       <c r="G539" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         </is>
       </c>
       <c r="B540">
-        <v>602.230086094847</v>
+        <v>602.2300860948469</v>
       </c>
       <c r="C540" t="inlineStr">
         <is>
@@ -20875,10 +20875,10 @@
         <v>1</v>
       </c>
       <c r="E540">
-        <v>1697.526032634345</v>
+        <v>1701.002582769084</v>
       </c>
       <c r="F540">
-        <v>798.5080333184362</v>
+        <v>800.1433856826741</v>
       </c>
       <c r="G540" t="inlineStr">
         <is>
@@ -20913,10 +20913,10 @@
         <v>0</v>
       </c>
       <c r="E541">
-        <v>2148.392968616527</v>
+        <v>2152.792898703565</v>
       </c>
       <c r="F541">
-        <v>798.508033318436</v>
+        <v>800.1433856826741</v>
       </c>
       <c r="G541" t="inlineStr">
         <is>
@@ -20951,10 +20951,10 @@
         <v>1</v>
       </c>
       <c r="E542">
-        <v>1780.213679749124</v>
+        <v>1783.464096505158</v>
       </c>
       <c r="F542">
-        <v>808.8760390708215</v>
+        <v>810.3529315702209</v>
       </c>
       <c r="G542" t="inlineStr">
         <is>
@@ -20989,10 +20989,10 @@
         <v>1</v>
       </c>
       <c r="E543">
-        <v>1719.56708787337</v>
+        <v>1722.706772586013</v>
       </c>
       <c r="F543">
-        <v>808.8760390708217</v>
+        <v>810.352931570221</v>
       </c>
       <c r="G543" t="inlineStr">
         <is>
@@ -21027,10 +21027,10 @@
         <v>0</v>
       </c>
       <c r="E544">
-        <v>2176.288180345873</v>
+        <v>2180.261772756616</v>
       </c>
       <c r="F544">
-        <v>808.8760390708218</v>
+        <v>810.3529315702209</v>
       </c>
       <c r="G544" t="inlineStr">
         <is>
@@ -21635,10 +21635,10 @@
         <v>1</v>
       </c>
       <c r="E560">
-        <v>2039.542608568693</v>
+        <v>2039.542608568692</v>
       </c>
       <c r="F560">
-        <v>926.7073753571557</v>
+        <v>926.7073753571555</v>
       </c>
       <c r="G560" t="inlineStr">
         <is>
@@ -21673,10 +21673,10 @@
         <v>1</v>
       </c>
       <c r="E561">
-        <v>1970.061450434626</v>
+        <v>1970.061450434625</v>
       </c>
       <c r="F561">
-        <v>926.7073753571557</v>
+        <v>926.7073753571555</v>
       </c>
       <c r="G561" t="inlineStr">
         <is>
@@ -21711,10 +21711,10 @@
         <v>0</v>
       </c>
       <c r="E562">
-        <v>2493.314439065172</v>
+        <v>2493.314439065171</v>
       </c>
       <c r="F562">
-        <v>926.7073753571557</v>
+        <v>926.7073753571555</v>
       </c>
       <c r="G562" t="inlineStr">
         <is>
@@ -21749,10 +21749,10 @@
         <v>1</v>
       </c>
       <c r="E563">
-        <v>2157.63674801456</v>
+        <v>2157.636748014559</v>
       </c>
       <c r="F563">
-        <v>980.3658326755556</v>
+        <v>980.3658326755553</v>
       </c>
       <c r="G563" t="inlineStr">
         <is>
@@ -21787,10 +21787,10 @@
         <v>1</v>
       </c>
       <c r="E564">
-        <v>2084.132473352762</v>
+        <v>2084.132473352761</v>
       </c>
       <c r="F564">
-        <v>980.3658326755558</v>
+        <v>980.3658326755553</v>
       </c>
       <c r="G564" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         </is>
       </c>
       <c r="B565">
-        <v>747.3635827251776</v>
+        <v>747.3635827251777</v>
       </c>
       <c r="C565" t="inlineStr">
         <is>
@@ -21825,10 +21825,10 @@
         <v>0</v>
       </c>
       <c r="E565">
-        <v>2637.68299592312</v>
+        <v>2637.682995923119</v>
       </c>
       <c r="F565">
-        <v>980.3658326755557</v>
+        <v>980.3658326755553</v>
       </c>
       <c r="G565" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         </is>
       </c>
       <c r="B566">
-        <v>611.3468270099368</v>
+        <v>611.3468270099366</v>
       </c>
       <c r="C566" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>1</v>
       </c>
       <c r="E566">
-        <v>2209.850021633253</v>
+        <v>2209.850021633252</v>
       </c>
       <c r="F566">
         <v>1004.0899880576</v>
@@ -21928,7 +21928,7 @@
         </is>
       </c>
       <c r="B568">
-        <v>747.3635827251779</v>
+        <v>747.3635827251778</v>
       </c>
       <c r="C568" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>0</v>
       </c>
       <c r="E568">
-        <v>2701.513047071553</v>
+        <v>2701.513047071552</v>
       </c>
       <c r="F568">
         <v>1004.0899880576</v>
@@ -21966,7 +21966,7 @@
         </is>
       </c>
       <c r="B569">
-        <v>611.3468270099368</v>
+        <v>611.3468270099366</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         </is>
       </c>
       <c r="B570">
-        <v>590.5200566430029</v>
+        <v>590.5200566430027</v>
       </c>
       <c r="C570" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         </is>
       </c>
       <c r="B571">
-        <v>747.3635827251779</v>
+        <v>747.3635827251777</v>
       </c>
       <c r="C571" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         </is>
       </c>
       <c r="B574">
-        <v>747.3635827251777</v>
+        <v>747.3635827251779</v>
       </c>
       <c r="C574" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>0</v>
       </c>
       <c r="E574">
-        <v>2845.506133038208</v>
+        <v>2845.506133038209</v>
       </c>
       <c r="F574">
         <v>1057.60889152</v>
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="B576">
-        <v>590.5200566430028</v>
+        <v>590.5200566430029</v>
       </c>
       <c r="C576" t="inlineStr">
         <is>
@@ -22243,10 +22243,10 @@
         <v>1</v>
       </c>
       <c r="E576">
-        <v>2303.374309340869</v>
+        <v>2303.37430934087</v>
       </c>
       <c r="F576">
-        <v>1083.496131657955</v>
+        <v>1083.496131657956</v>
       </c>
       <c r="G576" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         </is>
       </c>
       <c r="B577">
-        <v>747.3635827251777</v>
+        <v>747.3635827251778</v>
       </c>
       <c r="C577" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>2915.155982969138</v>
       </c>
       <c r="F577">
-        <v>1083.496131657955</v>
+        <v>1083.496131657956</v>
       </c>
       <c r="G577" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>0</v>
       </c>
       <c r="E580">
-        <v>3026.670837028466</v>
+        <v>3026.670837028467</v>
       </c>
       <c r="F580">
         <v>1124.943626646756</v>
@@ -22661,10 +22661,10 @@
         <v>1</v>
       </c>
       <c r="E587">
-        <v>2564.286008422001</v>
+        <v>2564.286008422</v>
       </c>
       <c r="F587">
-        <v>1165.135136940089</v>
+        <v>1165.135136940088</v>
       </c>
       <c r="G587" t="inlineStr">
         <is>
@@ -22699,10 +22699,10 @@
         <v>1</v>
       </c>
       <c r="E588">
-        <v>2476.928401425411</v>
+        <v>2476.92840142541</v>
       </c>
       <c r="F588">
-        <v>1165.135136940089</v>
+        <v>1165.135136940088</v>
       </c>
       <c r="G588" t="inlineStr">
         <is>
@@ -22737,10 +22737,10 @@
         <v>0</v>
       </c>
       <c r="E589">
-        <v>3134.806453089128</v>
+        <v>3134.806453089127</v>
       </c>
       <c r="F589">
-        <v>1165.135136940089</v>
+        <v>1165.135136940088</v>
       </c>
       <c r="G589" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>1</v>
       </c>
       <c r="E591">
-        <v>2518.462714062268</v>
+        <v>2518.462714062267</v>
       </c>
       <c r="F591">
         <v>1184.672676666311</v>
@@ -22851,7 +22851,7 @@
         <v>0</v>
       </c>
       <c r="E592">
-        <v>3187.372377563857</v>
+        <v>3187.372377563856</v>
       </c>
       <c r="F592">
         <v>1184.672676666311</v>
@@ -22930,7 +22930,7 @@
         <v>2499.731117541661</v>
       </c>
       <c r="F594">
-        <v>1175.861424284294</v>
+        <v>1175.861424284295</v>
       </c>
       <c r="G594" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         </is>
       </c>
       <c r="B596">
-        <v>579.1706782199401</v>
+        <v>579.1706782199402</v>
       </c>
       <c r="C596" t="inlineStr">
         <is>
@@ -23003,10 +23003,10 @@
         <v>1</v>
       </c>
       <c r="E596">
-        <v>2523.767591448522</v>
+        <v>2523.767591448523</v>
       </c>
       <c r="F596">
-        <v>1146.724775867284</v>
+        <v>1146.724775867285</v>
       </c>
       <c r="G596" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         </is>
       </c>
       <c r="B597">
-        <v>559.4400536617923</v>
+        <v>559.4400536617921</v>
       </c>
       <c r="C597" t="inlineStr">
         <is>
@@ -23079,10 +23079,10 @@
         <v>0</v>
       </c>
       <c r="E598">
-        <v>3085.27321281084</v>
+        <v>3085.273212810841</v>
       </c>
       <c r="F598">
-        <v>1146.724775867284</v>
+        <v>1146.724775867285</v>
       </c>
       <c r="G598" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         </is>
       </c>
       <c r="B599">
-        <v>579.1706782199402</v>
+        <v>579.1706782199401</v>
       </c>
       <c r="C599" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>1</v>
       </c>
       <c r="E599">
-        <v>2459.964478182307</v>
+        <v>2459.964478182306</v>
       </c>
       <c r="F599">
         <v>1117.734542769853</v>
@@ -23144,7 +23144,7 @@
         </is>
       </c>
       <c r="B600">
-        <v>559.4400536617923</v>
+        <v>559.4400536617921</v>
       </c>
       <c r="C600" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>1</v>
       </c>
       <c r="E600">
-        <v>2376.16079582986</v>
+        <v>2376.160795829859</v>
       </c>
       <c r="F600">
         <v>1117.734542769853</v>
@@ -23182,7 +23182,7 @@
         </is>
       </c>
       <c r="B601">
-        <v>708.0286573185896</v>
+        <v>708.0286573185895</v>
       </c>
       <c r="C601" t="inlineStr">
         <is>
@@ -23193,10 +23193,10 @@
         <v>0</v>
       </c>
       <c r="E601">
-        <v>3007.274732712596</v>
+        <v>3007.274732712595</v>
       </c>
       <c r="F601">
-        <v>1117.734542769853</v>
+        <v>1117.734542769852</v>
       </c>
       <c r="G601" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>1</v>
       </c>
       <c r="E602">
-        <v>2391.650033673848</v>
+        <v>2391.650033673847</v>
       </c>
       <c r="F602">
         <v>1086.694495210442</v>
@@ -23307,7 +23307,7 @@
         <v>0</v>
       </c>
       <c r="E604">
-        <v>2923.761208565537</v>
+        <v>2923.761208565536</v>
       </c>
       <c r="F604">
         <v>1086.694495210442</v>
@@ -23334,7 +23334,7 @@
         </is>
       </c>
       <c r="B605">
-        <v>579.1706782199401</v>
+        <v>579.1706782199402</v>
       </c>
       <c r="C605" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         </is>
       </c>
       <c r="B606">
-        <v>559.4400536617921</v>
+        <v>559.4400536617923</v>
       </c>
       <c r="C606" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>2896.973851765291</v>
       </c>
       <c r="F607">
-        <v>1076.738253541053</v>
+        <v>1076.738253541052</v>
       </c>
       <c r="G607" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>1</v>
       </c>
       <c r="E608">
-        <v>2324.946778895396</v>
+        <v>2324.946778895397</v>
       </c>
       <c r="F608">
         <v>1056.386524244884</v>
@@ -23573,7 +23573,7 @@
         <v>1</v>
       </c>
       <c r="E611">
-        <v>2291.111794585981</v>
+        <v>2291.111794585982</v>
       </c>
       <c r="F611">
         <v>1041.012915783411</v>
@@ -23611,7 +23611,7 @@
         <v>1</v>
       </c>
       <c r="E612">
-        <v>2213.060421580261</v>
+        <v>2213.060421580262</v>
       </c>
       <c r="F612">
         <v>1041.012915783411</v>
@@ -23649,7 +23649,7 @@
         <v>0</v>
       </c>
       <c r="E613">
-        <v>2800.854512651064</v>
+        <v>2800.854512651065</v>
       </c>
       <c r="F613">
         <v>1041.012915783411</v>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="B614">
-        <v>579.1706782199401</v>
+        <v>579.1706782199402</v>
       </c>
       <c r="C614" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>0</v>
       </c>
       <c r="E616">
-        <v>2729.946803471173</v>
+        <v>2729.946803471172</v>
       </c>
       <c r="F616">
         <v>1014.658158422232</v>
@@ -23866,7 +23866,7 @@
         </is>
       </c>
       <c r="B619">
-        <v>708.0286573185895</v>
+        <v>708.0286573185896</v>
       </c>
       <c r="C619" t="inlineStr">
         <is>
@@ -23877,10 +23877,10 @@
         <v>0</v>
       </c>
       <c r="E619">
-        <v>2635.600157086533</v>
+        <v>2635.600157086534</v>
       </c>
       <c r="F619">
-        <v>979.5916895986525</v>
+        <v>979.5916895986527</v>
       </c>
       <c r="G619" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         </is>
       </c>
       <c r="B620">
-        <v>579.17067821994</v>
+        <v>579.1706782199401</v>
       </c>
       <c r="C620" t="inlineStr">
         <is>
@@ -23915,10 +23915,10 @@
         <v>1</v>
       </c>
       <c r="E620">
-        <v>2140.465554929556</v>
+        <v>2140.465554929557</v>
       </c>
       <c r="F620">
-        <v>972.563754303326</v>
+        <v>972.5637543033264</v>
       </c>
       <c r="G620" t="inlineStr">
         <is>
@@ -23953,10 +23953,10 @@
         <v>1</v>
       </c>
       <c r="E621">
-        <v>2067.546251808474</v>
+        <v>2067.546251808475</v>
       </c>
       <c r="F621">
-        <v>972.5637543033263</v>
+        <v>972.5637543033265</v>
       </c>
       <c r="G621" t="inlineStr">
         <is>
@@ -23991,10 +23991,10 @@
         <v>0</v>
       </c>
       <c r="E622">
-        <v>2616.69143464122</v>
+        <v>2616.691434641221</v>
       </c>
       <c r="F622">
-        <v>972.563754303326</v>
+        <v>972.5637543033264</v>
       </c>
       <c r="G622" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         </is>
       </c>
       <c r="B623">
-        <v>579.1706782199402</v>
+        <v>579.17067821994</v>
       </c>
       <c r="C623" t="inlineStr">
         <is>
@@ -24029,10 +24029,10 @@
         <v>1</v>
       </c>
       <c r="E623">
-        <v>2115.008757212034</v>
+        <v>2115.008757212033</v>
       </c>
       <c r="F623">
-        <v>960.9969441280001</v>
+        <v>960.9969441279999</v>
       </c>
       <c r="G623" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         </is>
       </c>
       <c r="B624">
-        <v>559.4400536617923</v>
+        <v>559.4400536617921</v>
       </c>
       <c r="C624" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>2042.956691568789</v>
       </c>
       <c r="F624">
-        <v>960.9969441280001</v>
+        <v>960.9969441279999</v>
       </c>
       <c r="G624" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         </is>
       </c>
       <c r="B625">
-        <v>708.0286573185896</v>
+        <v>708.0286573185895</v>
       </c>
       <c r="C625" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         </is>
       </c>
       <c r="B626">
-        <v>579.1706782199401</v>
+        <v>579.17067821994</v>
       </c>
       <c r="C626" t="inlineStr">
         <is>
@@ -24143,10 +24143,10 @@
         <v>1</v>
       </c>
       <c r="E626">
-        <v>2078.112512416494</v>
+        <v>2078.112512416493</v>
       </c>
       <c r="F626">
-        <v>944.2323901386109</v>
+        <v>944.2323901386104</v>
       </c>
       <c r="G626" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>2007.317392231717</v>
       </c>
       <c r="F627">
-        <v>944.2323901386109</v>
+        <v>944.2323901386108</v>
       </c>
       <c r="G627" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         </is>
       </c>
       <c r="B628">
-        <v>708.0286573185896</v>
+        <v>708.0286573185895</v>
       </c>
       <c r="C628" t="inlineStr">
         <is>
@@ -24219,10 +24219,10 @@
         <v>0</v>
       </c>
       <c r="E628">
-        <v>2540.46564726894</v>
+        <v>2540.465647268939</v>
       </c>
       <c r="F628">
-        <v>944.2323901386108</v>
+        <v>944.2323901386106</v>
       </c>
       <c r="G628" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         </is>
       </c>
       <c r="B629">
-        <v>579.17067821994</v>
+        <v>579.1706782199401</v>
       </c>
       <c r="C629" t="inlineStr">
         <is>
@@ -24257,10 +24257,10 @@
         <v>1</v>
       </c>
       <c r="E629">
-        <v>2048.466621404507</v>
+        <v>2048.466621404508</v>
       </c>
       <c r="F629">
-        <v>930.7621808208842</v>
+        <v>930.7621808208844</v>
       </c>
       <c r="G629" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>1978.681448662248</v>
       </c>
       <c r="F630">
-        <v>930.7621808208844</v>
+        <v>930.7621808208842</v>
       </c>
       <c r="G630" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         </is>
       </c>
       <c r="B632">
-        <v>579.1706782199402</v>
+        <v>579.17067821994</v>
       </c>
       <c r="C632" t="inlineStr">
         <is>
@@ -24371,10 +24371,10 @@
         <v>1</v>
       </c>
       <c r="E632">
-        <v>2041.055148650029</v>
+        <v>2041.055148650028</v>
       </c>
       <c r="F632">
-        <v>927.3946284907792</v>
+        <v>927.3946284907788</v>
       </c>
       <c r="G632" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         </is>
       </c>
       <c r="B635">
-        <v>579.17067821994</v>
+        <v>579.1706782199401</v>
       </c>
       <c r="C635" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>2027.360035955337</v>
       </c>
       <c r="F635">
-        <v>921.1719774477473</v>
+        <v>921.1719774477474</v>
       </c>
       <c r="G635" t="inlineStr">
         <is>
@@ -24523,10 +24523,10 @@
         <v>1</v>
       </c>
       <c r="E636">
-        <v>1958.293901881406</v>
+        <v>1958.293901881407</v>
       </c>
       <c r="F636">
-        <v>921.1719774477472</v>
+        <v>921.1719774477474</v>
       </c>
       <c r="G636" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         </is>
       </c>
       <c r="B637">
-        <v>708.0286573185895</v>
+        <v>708.0286573185896</v>
       </c>
       <c r="C637" t="inlineStr">
         <is>
